--- a/artfynd/A 12550-2026 artfynd.xlsx
+++ b/artfynd/A 12550-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131553758</v>
       </c>
       <c r="B2" t="n">
-        <v>101228</v>
+        <v>101231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12550-2026 artfynd.xlsx
+++ b/artfynd/A 12550-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131553758</v>
       </c>
       <c r="B2" t="n">
-        <v>101231</v>
+        <v>101237</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12550-2026 artfynd.xlsx
+++ b/artfynd/A 12550-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131553758</v>
       </c>
       <c r="B2" t="n">
-        <v>101237</v>
+        <v>101238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12550-2026 artfynd.xlsx
+++ b/artfynd/A 12550-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131553758</v>
       </c>
       <c r="B2" t="n">
-        <v>101238</v>
+        <v>101239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12550-2026 artfynd.xlsx
+++ b/artfynd/A 12550-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131553758</v>
       </c>
       <c r="B2" t="n">
-        <v>101239</v>
+        <v>101242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12550-2026 artfynd.xlsx
+++ b/artfynd/A 12550-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131553758</v>
       </c>
       <c r="B2" t="n">
-        <v>101242</v>
+        <v>101243</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12550-2026 artfynd.xlsx
+++ b/artfynd/A 12550-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131553758</v>
       </c>
       <c r="B2" t="n">
-        <v>101243</v>
+        <v>101249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12550-2026 artfynd.xlsx
+++ b/artfynd/A 12550-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131553758</v>
       </c>
       <c r="B2" t="n">
-        <v>101249</v>
+        <v>101252</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12550-2026 artfynd.xlsx
+++ b/artfynd/A 12550-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131553758</v>
       </c>
       <c r="B2" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12550-2026 artfynd.xlsx
+++ b/artfynd/A 12550-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131553758</v>
       </c>
       <c r="B2" t="n">
-        <v>101257</v>
+        <v>101260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 12550-2026 artfynd.xlsx
+++ b/artfynd/A 12550-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131553758</v>
       </c>
       <c r="B2" t="n">
-        <v>101260</v>
+        <v>101403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
